--- a/inputs/estimation.xlsx
+++ b/inputs/estimation.xlsx
@@ -11,36 +11,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Estimated Hours</t>
-  </si>
-  <si>
-    <t>Assigned To</t>
-  </si>
-  <si>
-    <t>Voice Bot Core</t>
-  </si>
-  <si>
-    <t>Team A</t>
-  </si>
-  <si>
-    <t>Multilingual Setup</t>
-  </si>
-  <si>
-    <t>Team B</t>
-  </si>
-  <si>
-    <t>IT Helpdesk Flow</t>
-  </si>
-  <si>
-    <t>Team C</t>
-  </si>
-  <si>
-    <t>HRDB Integration</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>Sl no</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Est. Hours</t>
+  </si>
+  <si>
+    <t>Requirement Analysis &amp; Planning</t>
+  </si>
+  <si>
+    <t>Requirement Gathering</t>
+  </si>
+  <si>
+    <t>Understanding legacy system structure and target framework</t>
+  </si>
+  <si>
+    <t>Feasibility Study</t>
+  </si>
+  <si>
+    <t>Analyze what parts can be modernized via AI</t>
+  </si>
+  <si>
+    <t>Architecture Planning</t>
+  </si>
+  <si>
+    <t>Define backend &amp; frontend folder structures, API contracts</t>
+  </si>
+  <si>
+    <t>Frontend Development</t>
+  </si>
+  <si>
+    <t>UI Design</t>
+  </si>
+  <si>
+    <t>High-level wireframes &amp; screens for input/upload and results</t>
+  </si>
+  <si>
+    <t>React Frontend Setup</t>
+  </si>
+  <si>
+    <t>Initializing folder structure, routing, theming</t>
+  </si>
+  <si>
+    <t>User Input Page</t>
+  </si>
+  <si>
+    <t>Page to upload legacy code and specify framework</t>
+  </si>
+  <si>
+    <t>Output Viewer</t>
+  </si>
+  <si>
+    <t>Display AI-generated modernized code</t>
+  </si>
+  <si>
+    <t>API Integration</t>
+  </si>
+  <si>
+    <t>Call backend services for transformation</t>
+  </si>
+  <si>
+    <t>Backend Development</t>
+  </si>
+  <si>
+    <t>FastAPI Setup</t>
+  </si>
+  <si>
+    <t>Environment setup, folder structure</t>
+  </si>
+  <si>
+    <t>Upload &amp; Parse Legacy Code</t>
+  </si>
+  <si>
+    <t>Accept code, extract structure</t>
+  </si>
+  <si>
+    <t>AI Integration Logic</t>
+  </si>
+  <si>
+    <t>Prompt creation, sending to GPT/OpenAI API</t>
+  </si>
+  <si>
+    <t>Code Generator</t>
+  </si>
+  <si>
+    <t>Receive and store modernized code</t>
+  </si>
+  <si>
+    <t>Logging &amp; Error Handling</t>
+  </si>
+  <si>
+    <t>Robustness &amp; maintainability</t>
+  </si>
+  <si>
+    <t>AI Prompt Design &amp; Optimization</t>
+  </si>
+  <si>
+    <t>Prompt Design</t>
+  </si>
+  <si>
+    <t>Effective prompt structure for legacy-to-modern conversion</t>
+  </si>
+  <si>
+    <t>Test &amp; Tuning</t>
+  </si>
+  <si>
+    <t>Refine prompts for different legacy formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Testing &amp; Deployment</t>
+  </si>
+  <si>
+    <t>Unit Testing</t>
+  </si>
+  <si>
+    <t>Frontend &amp; backend unit tests</t>
+  </si>
+  <si>
+    <t>Integration Testing</t>
+  </si>
+  <si>
+    <t>End-to-end flow test from upload to result</t>
+  </si>
+  <si>
+    <t>Dockerization</t>
+  </si>
+  <si>
+    <t>Containerize backend for portability</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Setup on cloud (e.g., Azure/AWS)</t>
+  </si>
+  <si>
+    <t>Documentation &amp; Buffer</t>
+  </si>
+  <si>
+    <t>Technical Docs</t>
+  </si>
+  <si>
+    <t>README, architecture flow, API usage</t>
+  </si>
+  <si>
+    <t>User Guide</t>
+  </si>
+  <si>
+    <t>Guide for using the app effectively</t>
+  </si>
+  <si>
+    <t>Buffer</t>
+  </si>
+  <si>
+    <t>For unplanned changes/feedback</t>
   </si>
 </sst>
 </file>
@@ -74,21 +209,53 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -303,9 +470,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.5"/>
-    <col customWidth="1" min="2" max="2" width="20.25"/>
-    <col customWidth="1" min="3" max="3" width="23.88"/>
+    <col customWidth="1" min="1" max="1" width="10.25"/>
+    <col customWidth="1" min="2" max="2" width="22.88"/>
+    <col customWidth="1" min="3" max="3" width="25.0"/>
+    <col customWidth="1" min="4" max="4" width="49.25"/>
+    <col customWidth="1" min="5" max="5" width="11.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -318,50 +487,364 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>40.0</v>
+      <c r="A2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2">
-        <v>20.0</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2">
+        <v>6.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2">
-        <v>15.0</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2">
-        <v>25.0</v>
+      <c r="A5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
